--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136370093</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>136390574</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136390613</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136391139</v>
       </c>
       <c r="B26" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136391147</v>
       </c>
       <c r="B27" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136391158</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>136391189</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136391199</v>
       </c>
       <c r="B30" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136391288</v>
       </c>
       <c r="B31" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136352733</v>
       </c>
       <c r="B40" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>136369839</v>
       </c>
       <c r="B41" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136391215</v>
       </c>
       <c r="B42" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>136405709</v>
       </c>
       <c r="B43" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>136369811</v>
       </c>
       <c r="B45" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>136369816</v>
       </c>
       <c r="B46" t="n">
-        <v>79151</v>
+        <v>79153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>136369808</v>
       </c>
       <c r="B47" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6090,32 +6090,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136352733</v>
+        <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6123,28 +6123,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521191</v>
+        <v>521244</v>
       </c>
       <c r="R40" t="n">
-        <v>6637198</v>
+        <v>6637117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6171,17 +6164,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i tallåga</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6195,75 +6183,55 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136940465</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136369839</v>
+        <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6271,31 +6239,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521218</v>
+        <v>521254</v>
       </c>
       <c r="R41" t="n">
-        <v>6637248</v>
+        <v>6637306</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6319,17 +6280,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>hackmärken i talltorraka</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6343,100 +6299,77 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136940467</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136391215</v>
+        <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521254</v>
+        <v>521255</v>
       </c>
       <c r="R42" t="n">
-        <v>6637318</v>
+        <v>6637251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6463,17 +6396,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>färska hackmärken i tallåga</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6487,75 +6415,55 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391215</t>
+          <t>https://artportalen.se/Sighting/136940468</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136405709</v>
+        <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6563,28 +6471,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521325</v>
+        <v>521243</v>
       </c>
       <c r="R43" t="n">
-        <v>6637266</v>
+        <v>6637351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6611,17 +6512,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>hackmärken i murken tallåga</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6635,53 +6531,33 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136405709</t>
+          <t>https://artportalen.se/Sighting/136940469</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136370107</v>
+        <v>136352733</v>
       </c>
       <c r="B44" t="n">
-        <v>106369</v>
+        <v>58005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6689,42 +6565,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221154</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521195</v>
+        <v>521191</v>
       </c>
       <c r="R44" t="n">
-        <v>6637298</v>
+        <v>6637198</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6759,19 +6643,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i tallåga</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6788,16 +6696,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136352733</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136369811</v>
+        <v>136369839</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>58005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6805,27 +6713,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228595</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
@@ -6838,7 +6759,7 @@
         <v>6637248</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6870,19 +6791,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>hackmärken i talltorraka</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6899,16 +6844,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136369839</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136369816</v>
+        <v>136391215</v>
       </c>
       <c r="B46" t="n">
-        <v>79153</v>
+        <v>58005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6916,37 +6861,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228654</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521218</v>
+        <v>521254</v>
       </c>
       <c r="R46" t="n">
-        <v>6637248</v>
+        <v>6637318</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6981,19 +6935,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>färska hackmärken i tallåga</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7010,16 +6988,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136391215</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136369808</v>
+        <v>136405709</v>
       </c>
       <c r="B47" t="n">
-        <v>79160</v>
+        <v>58005</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7027,37 +7005,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228659</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521218</v>
+        <v>521325</v>
       </c>
       <c r="R47" t="n">
-        <v>6637248</v>
+        <v>6637266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7092,19 +7083,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>hackmärken i murken tallåga</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7120,6 +7135,567 @@
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136405709</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136940463</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>521221</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6637195</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940463</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79153</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -7173,6 +7749,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6554,32 +6554,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136352733</v>
+        <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6587,31 +6587,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521191</v>
+        <v>521307</v>
       </c>
       <c r="R44" t="n">
-        <v>6637198</v>
+        <v>6637293</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6635,17 +6623,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hackmärken i tallåga</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6656,78 +6654,53 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/137007762</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136369839</v>
+        <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6735,31 +6708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521218</v>
+        <v>521310</v>
       </c>
       <c r="R45" t="n">
-        <v>6637248</v>
+        <v>6637284</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6783,17 +6744,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>hackmärken i talltorraka</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6804,53 +6775,28 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/137007764</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136391215</v>
+        <v>136352733</v>
       </c>
       <c r="B46" t="n">
         <v>58005</v>
@@ -6878,7 +6824,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
@@ -6893,14 +6843,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521254</v>
+        <v>521191</v>
       </c>
       <c r="R46" t="n">
-        <v>6637318</v>
+        <v>6637198</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6937,7 +6887,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>färska hackmärken i tallåga</t>
+          <t>Färska hackmärken i tallåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6988,13 +6938,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391215</t>
+          <t>https://artportalen.se/Sighting/136352733</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136405709</v>
+        <v>136369839</v>
       </c>
       <c r="B47" t="n">
         <v>58005</v>
@@ -7041,17 +6991,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521325</v>
+        <v>521218</v>
       </c>
       <c r="R47" t="n">
-        <v>6637266</v>
+        <v>6637248</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7085,7 +7035,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>hackmärken i murken tallåga</t>
+          <t>hackmärken i talltorraka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7114,12 +7064,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7136,33 +7086,33 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136405709</t>
+          <t>https://artportalen.se/Sighting/136369839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136940463</v>
+        <v>136391215</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7171,21 +7121,28 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521221</v>
+        <v>521254</v>
       </c>
       <c r="R48" t="n">
-        <v>6637195</v>
+        <v>6637318</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7212,12 +7169,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>färska hackmärken i tallåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7231,33 +7193,53 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136940463</t>
+          <t>https://artportalen.se/Sighting/136391215</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136370107</v>
+        <v>136405709</v>
       </c>
       <c r="B49" t="n">
-        <v>106369</v>
+        <v>58005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7265,42 +7247,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221154</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521195</v>
+        <v>521325</v>
       </c>
       <c r="R49" t="n">
-        <v>6637298</v>
+        <v>6637266</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7335,19 +7325,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hackmärken i murken tallåga</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7364,54 +7378,56 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136405709</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136369811</v>
+        <v>136940463</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228595</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521218</v>
+        <v>521221</v>
       </c>
       <c r="R50" t="n">
-        <v>6637248</v>
+        <v>6637195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7438,12 +7454,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7452,80 +7468,80 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136940463</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136369816</v>
+        <v>137007622</v>
       </c>
       <c r="B51" t="n">
-        <v>79153</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228654</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521218</v>
+        <v>521225</v>
       </c>
       <c r="R51" t="n">
-        <v>6637248</v>
+        <v>6637195</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7549,12 +7565,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7563,80 +7594,75 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/137007622</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136369808</v>
+        <v>137007629</v>
       </c>
       <c r="B52" t="n">
-        <v>79160</v>
+        <v>58169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228659</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521218</v>
+        <v>521301</v>
       </c>
       <c r="R52" t="n">
-        <v>6637248</v>
+        <v>6637264</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7660,12 +7686,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7674,28 +7715,471 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137007629</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79153</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -7754,6 +8238,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136370093</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>136390574</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136390613</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136391139</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136391147</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136391158</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>136391189</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136391199</v>
       </c>
       <c r="B30" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136391288</v>
       </c>
       <c r="B31" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>136370107</v>
       </c>
       <c r="B53" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136369811</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136369816</v>
       </c>
       <c r="B55" t="n">
-        <v>79153</v>
+        <v>79157</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>136369808</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>79164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136370093</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>136390574</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136390613</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136391139</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136391147</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136391158</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>136391189</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136391199</v>
       </c>
       <c r="B30" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136391288</v>
       </c>
       <c r="B31" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>136370107</v>
       </c>
       <c r="B53" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136369811</v>
       </c>
       <c r="B54" t="n">
-        <v>79080</v>
+        <v>79082</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136369816</v>
       </c>
       <c r="B55" t="n">
-        <v>79157</v>
+        <v>79159</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>136369808</v>
       </c>
       <c r="B56" t="n">
-        <v>79164</v>
+        <v>79166</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>136940463</v>
       </c>
       <c r="B50" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>137007622</v>
       </c>
       <c r="B51" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137007629</v>
       </c>
       <c r="B52" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -6093,7 +6093,7 @@
         <v>136940465</v>
       </c>
       <c r="B40" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136940467</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136940468</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136940469</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>137007762</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>137007764</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>136940463</v>
       </c>
       <c r="B50" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>137007622</v>
       </c>
       <c r="B51" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137007629</v>
       </c>
       <c r="B52" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
